--- a/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
+++ b/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
@@ -1049,7 +1049,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Every task uses the Inventory sheet: supply stock in 15 storerooms across three Bluestone hospitals, counted on 12/31/2025. Do the tasks in order, because later tasks use the Table, columns, Total Row, and names you create in earlier ones. After task 1, write formulas with structured references such as tblInventory[QtyOnHand] instead of cell ranges.</t>
+          <t>The tasks use the Inventory sheet: supply stock in 15 storerooms across three Bluestone hospitals, in the snapshot taken on 12/31/2025. Task 9 also uses the Settings sheet. Do the tasks in order, because later tasks use the Table, columns, Total Row, and names you create in earlier ones. After task 1, write formulas with structured references such as tblInventory[QtyOnHand] instead of cell ranges.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>On the Inventory sheet, click any cell in the data and convert the range to an Excel Table (Ctrl + T; Mac: Control + T). Then rename the Table tblInventory in the Table Name box on the Table Design tab. The gray cell finds a Table with that exact name and counts its data rows. It stays blank until the Table exists.</t>
+          <t>On the Inventory sheet, click any cell in the data and convert the range to an Excel Table with Ctrl + T (Mac: Control + T). Then rename the Table tblInventory in the Table Name box on the Table Design tab (Mac: Table tab). The gray cell finds a Table with that exact name and counts its data rows. It stays blank until the Table exists.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Click the QtyOnHand cell in the same row while typing; Excel writes [@QtyOnHand]</t>
+          <t>Click the QtyOnHand cell in the same row while you type, and Excel writes [@QtyOnHand]</t>
         </is>
       </c>
       <c r="D8" cm="1" s="24">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Policy says every stock row must be cycle-counted at least every 30 days. Create a named constant CycleCountDays that refers to =30 (Formulas → Define Name; it doesn't live in any cell). How many rows are overdue, meaning ReportDate − LastCountDate is greater than CycleCountDays?</t>
+          <t>Policy says every stock row must be cycle-counted at least every 30 days. Create a named constant CycleCountDays that refers to =30 with Formulas → Define Name. It doesn't live in any cell. How many rows are overdue, meaning ReportDate − LastCountDate is greater than CycleCountDays?</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -19377,7 +19377,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Task 9 names B2 and B3 from the labels in column A. Later tasks and the bonus add named constants (CycleCountDays, DiscountMin, DiscountPct) in Name Manager; they don't live in cells.</t>
+          <t>Task 9 names B2 and B3 from the labels in column A. Task 12 and the bonus add named constants (CycleCountDays, DiscountMin, DiscountPct) with Formulas → Define Name. Named constants don't live in cells.</t>
         </is>
       </c>
     </row>
@@ -19660,7 +19660,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>The group purchasing contract gives a 2% discount on any single vendor order of $20,000 or more. Define two named constants, DiscountMin (=20000) and DiscountPct (=0.02), then calculate the total discount on this week's orders.</t>
+          <t>The group purchasing contract gives a 2% discount on any single vendor order of $20,000 or more. Define two named constants, DiscountMin (=20000) and DiscountPct (=0.02), then calculate the total discount on this week's orders, to the cent.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>On the Inventory sheet, click any cell in the data and convert the range to an Excel Table (Ctrl + T; Mac: Control + T). Then rename the Table tblInventory in the Table Name box on the Table Design tab. The gray cell finds a Table with that exact name and counts its data rows. It stays blank until the Table exists.</t>
+          <t>On the Inventory sheet, click any cell in the data and convert the range to an Excel Table with Ctrl + T (Mac: Control + T). Then rename the Table tblInventory in the Table Name box on the Table Design tab (Mac: Table tab). The gray cell finds a Table with that exact name and counts its data rows. It stays blank until the Table exists.</t>
         </is>
       </c>
       <c r="C5" s="42" t="n">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Policy says every stock row must be cycle-counted at least every 30 days. Create a named constant CycleCountDays that refers to =30 (Formulas → Define Name; it doesn't live in any cell). How many rows are overdue, meaning ReportDate − LastCountDate is greater than CycleCountDays?</t>
+          <t>Policy says every stock row must be cycle-counted at least every 30 days. Create a named constant CycleCountDays that refers to =30 with Formulas → Define Name. It doesn't live in any cell. How many rows are overdue, meaning ReportDate − LastCountDate is greater than CycleCountDays?</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -20226,7 +20226,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="141" customHeight="1">
+    <row r="6" ht="156" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -20254,7 +20254,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from *another* Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) works too in Excel 2021 or Microsoft 365. Orthopedic implants cost thousands of dollars each, so even a few reorder lines make the largest order.</t>
+          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from *another* Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) works too in Excel 2021 or Microsoft 365. All four reorder lines for Summit Orthopedic Systems are orthopedic implants, and three of them cost more than $2,000 per unit, so a handful of lines makes the largest order.</t>
         </is>
       </c>
     </row>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>The group purchasing contract gives a 2% discount on any single vendor order of $20,000 or more. Define two named constants, DiscountMin (=20000) and DiscountPct (=0.02), then calculate the total discount on this week's orders.</t>
+          <t>The group purchasing contract gives a 2% discount on any single vendor order of $20,000 or more. Define two named constants, DiscountMin (=20000) and DiscountPct (=0.02), then calculate the total discount on this week's orders, to the cent.</t>
         </is>
       </c>
       <c r="C8" s="45" t="n">

--- a/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
+++ b/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Table Design → Total Row (Windows: Ctrl + Shift + T), then use the dropdown in the Total Row cell</t>
+          <t>Table Design → Total Row (Windows: Ctrl + Shift + T; Mac: Table → Total Row), then use the dropdown in the Total Row cell</t>
         </is>
       </c>
       <c r="D11" s="26" t="n"/>
@@ -1256,7 +1256,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="81" customHeight="1">
+    <row r="13" ht="96" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Insert slicers for Facility and Category (Table Design → Insert Slicer). Select Cedar Ridge Medical Center in the Facility slicer and Surgical in the Category slicer. Set the Total Row's ExtendedValue cell to Sum. What value does it show? Type the number, then clear both slicers, because while they filter the Table the Total Row (and task 6) only summarizes the visible rows.</t>
+          <t>Insert slicers for Facility and Category (Table Design → Insert Slicer; Mac: Table → Insert Slicer). Select Cedar Ridge Medical Center in the Facility slicer and Surgical in the Category slicer. Set the Total Row's ExtendedValue cell to Sum. What value does it show? Type the number, then clear both slicers, because while they filter the Table the Total Row (and task 6) only summarizes the visible rows.</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Expired stock must be pulled from the shelves and written off. What's the total ExtendedValue of rows whose ExpirationDate is before ReportDate?</t>
+          <t>Expired stock must be pulled from the shelves and written off. What's the total ExtendedValue of rows whose ExpirationDate is before ReportDate? Enter it to the cent.</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -19319,12 +19319,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19377,7 +19377,21 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Task 9 names B2 and B3 from the labels in column A. Task 12 and the bonus add named constants (CycleCountDays, DiscountMin, DiscountPct) with Formulas → Define Name. Named constants don't live in cells.</t>
+          <t>Task 9 names B2 and B3 after the labels in column A (Formulas → Create from Selection).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Task 12 and the bonus add named constants (CycleCountDays, DiscountMin, DiscountPct) with Formulas → Define Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Named constants live only in Name Manager, so you won't see them on this sheet.</t>
         </is>
       </c>
     </row>
@@ -19604,7 +19618,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>IF can test a TRUE/FALSE column directly: IF([@NeedsReorder], …, 0)</t>
+          <t>IF's test can be the TRUE/FALSE value in [@NeedsReorder] itself, with no comparison needed</t>
         </is>
       </c>
       <c r="D6" cm="1" s="24">
@@ -19646,7 +19660,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>What's the value of that vendor's purchase order?</t>
+          <t>What's the value of that vendor's purchase order, to the cent?</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -19942,7 +19956,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="66" customHeight="1">
+    <row r="11" ht="81" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>7</t>
@@ -19968,7 +19982,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>[#All] covers the header row, the 257 data rows, and the Total Row: 1 + 257 + 1 = 259. tblInventory[#Data] (or just tblInventory) is the 257 data rows, [#Headers] is the header row alone, and [#Totals] is the Total Row alone.</t>
+          <t>ROWS counts the rows a reference covers. [#All] covers the header row, the 257 data rows, and the Total Row: 1 + 257 + 1 = 259. tblInventory[#Data] (or just tblInventory) is the 257 data rows, [#Headers] is the header row alone, and [#Totals] is the Total Row alone.</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19994,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Insert slicers for Facility and Category (Table Design → Insert Slicer). Select Cedar Ridge Medical Center in the Facility slicer and Surgical in the Category slicer. Set the Total Row's ExtendedValue cell to Sum. What value does it show? Type the number, then clear both slicers, because while they filter the Table the Total Row (and task 6) only summarizes the visible rows.</t>
+          <t>Insert slicers for Facility and Category (Table Design → Insert Slicer; Mac: Table → Insert Slicer). Select Cedar Ridge Medical Center in the Facility slicer and Surgical in the Category slicer. Set the Total Row's ExtendedValue cell to Sum. What value does it show? Type the number, then clear both slicers, because while they filter the Table the Total Row (and task 6) only summarizes the visible rows.</t>
         </is>
       </c>
       <c r="C12" s="45" t="n">
@@ -20074,7 +20088,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Expired stock must be pulled from the shelves and written off. What's the total ExtendedValue of rows whose ExpirationDate is before ReportDate?</t>
+          <t>Expired stock must be pulled from the shelves and written off. What's the total ExtendedValue of rows whose ExpirationDate is before ReportDate? Enter it to the cent.</t>
         </is>
       </c>
       <c r="C15" s="45" t="n">
@@ -20258,7 +20272,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>B3</t>
@@ -20266,7 +20280,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>What's the value of that vendor's purchase order?</t>
+          <t>What's the value of that vendor's purchase order, to the cent?</t>
         </is>
       </c>
       <c r="C7" s="45" t="n">
@@ -20283,11 +20297,11 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>That's 36% of the week's spend on a single purchase order. In practice, a buyer would confirm implant orders with the OR schedule before sending them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="81" customHeight="1">
+          <t>MAX scans the ReorderCost column of tblVendors, so it returns the largest vendor total, the same row that INDEX/MATCH found in B2. That's 36% of the week's spend on a single purchase order. In practice, a buyer would confirm implant orders with the OR schedule before sending them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="111" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -20313,7 +20327,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Orders from 3 vendors reach $20,000. Together they total $121,583.18, and 2% of that is the discount. With the thresholds in named constants, Purchasing can test a new contract (say 3% at $15,000) by editing two names in Name Manager, and every formula that uses them updates.</t>
+          <t>The criteria range and the sum range are the same column, so SUMIFS adds only the vendor totals that pass the test against DiscountMin. Orders from 3 vendors reach $20,000. Together they total $121,583.18, and 2% of that is the discount. With the thresholds in named constants, Purchasing can test a new contract (say 3% at $15,000) by editing two names in Name Manager, and every formula that uses them updates.</t>
         </is>
       </c>
     </row>

--- a/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
+++ b/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,32 +310,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -852,7 +849,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -920,7 +917,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -944,7 +941,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1154,7 @@
         </is>
       </c>
       <c r="D8" cm="1" s="24">
-        <f t="array" ref="D8">IF(COUNT('Inventory'!$R$2:$R$258)=0,"",SUM('Inventory'!$R$2:$R$258))</f>
+        <f t="array" ref="D8">IF(COUNT(Inventory!$R$2:$R$258)=0,"",SUM(Inventory!$R$2:$R$258))</f>
         <v/>
       </c>
       <c r="E8" s="22">
@@ -1204,7 +1201,7 @@
         </is>
       </c>
       <c r="D10" cm="1" s="21">
-        <f t="array" ref="D10">IF(COUNTA('Inventory'!$S$2:$S$258)=0,"",COUNTIF('Inventory'!$S$2:$S$258,TRUE))</f>
+        <f t="array" ref="D10">IF(COUNTA(Inventory!$S$2:$S$258)=0,"",COUNTIF(Inventory!$S$2:$S$258,TRUE))</f>
         <v/>
       </c>
       <c r="E10" s="22">
@@ -19729,7 +19726,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -19743,7 +19740,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -19779,7 +19776,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="171" customHeight="1">
+    <row r="5" ht="156" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>1</t>
@@ -19795,14 +19792,14 @@
       </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>1. Click any cell inside the data, for example **A2**.
-2. Press **Ctrl + T** (Mac: **Control + T**), or choose **Insert → Table**.
-3. Check that the range shows **$A$1:$S$258** and that **My table has headers** is ticked, then click **OK**.
-4. On the **Table Design** tab (Mac: **Table** tab), click in the **Table Name** box at the far left, type `tblInventory`, and press **Enter**.</t>
-        </is>
-      </c>
-      <c r="E5" cm="1" s="44">
-        <f t="array" ref="E5">COUNTA('Inventory'!$A$2:$A$258)</f>
+          <t>1. Click any cell inside the data, for example A2.
+2. Press Ctrl + T (Mac: Control + T), or choose Insert → Table.
+3. Check that the range shows $A$1:$S$258 and that My table has headers is ticked, then click OK.
+4. On the Table Design tab (Mac: Table tab), click in the Table Name box at the far left, type tblInventory, and press Enter.</t>
+        </is>
+      </c>
+      <c r="E5" cm="1" s="19">
+        <f t="array" ref="E5">COUNTA(Inventory!$A$2:$A$258)</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -19830,13 +19827,13 @@
           <t>=COUNTIF(tblInventory[QtyOnHand],0)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="44">
-        <f t="array" ref="E6">COUNTIF('Inventory'!$J$2:$J$258,0)</f>
+      <c r="E6" cm="1" s="19">
+        <f t="array" ref="E6">COUNTIF(Inventory!$J$2:$J$258,0)</f>
         <v/>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>tblInventory[QtyOnHand] means "every data cell in the QtyOnHand column." It excludes the header and the Total Row, and it grows when rows are added. After you type tblInventory[, Excel lists the columns. Pick one with the arrow keys and press Tab. These rows are *stockouts*: a nurse who reaches for the item finds an empty bin.</t>
+          <t>tblInventory[QtyOnHand] means "every data cell in the QtyOnHand column." It excludes the header and the Total Row, and it grows when rows are added. After you type tblInventory[, Excel lists the columns. Pick one with the arrow keys and press Tab. These rows are stockouts: a nurse who reaches for the item finds an empty bin.</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19848,7 @@
           <t>Fill the yellow ExtendedValue column (column R) with a calculated column: each row's QtyOnHand × UnitCost. Type the formula once in R2 and press Enter, and the Table fills every row. The gray cell totals the column: what's the value of all stock on hand across the system?</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="44" t="n">
         <v>1011928.89</v>
       </c>
       <c r="D7" s="43" t="inlineStr">
@@ -19859,13 +19856,13 @@
           <t>=[@QtyOnHand]*[@UnitCost]</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="46">
-        <f t="array" ref="E7">SUMPRODUCT('Inventory'!$J$2:$J$258,'Inventory'!$G$2:$G$258)</f>
+      <c r="E7" cm="1" s="45">
+        <f t="array" ref="E7">SUMPRODUCT(Inventory!$J$2:$J$258,Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>When you enter a formula in an empty Table column, Excel copies it to every row of that column. That's a *calculated column*. [@QtyOnHand] means "QtyOnHand in this row," so the formula reads the same on all 257 rows and says what it multiplies. The A1 version, =J2*G2, changes on every row and tells the next reader nothing about the columns it uses.</t>
+          <t>When you enter a formula in an empty Table column, Excel copies it to every row of that column. That's a calculated column. [@QtyOnHand] means "QtyOnHand in this row," so the formula reads the same on all 257 rows and says what it multiplies. The A1 version, =J2*G2, changes on every row and tells the next reader nothing about the columns it uses.</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19877,7 @@
           <t>What share of the system's total inventory value (ExtendedValue) is Orthopedic Implants stock? Divide the category's value by the total of all rows and enter it as a percentage, to 1 decimal place.</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="46" t="n">
         <v>0.1400812363406286</v>
       </c>
       <c r="D8" s="43" t="inlineStr">
@@ -19888,8 +19885,8 @@
           <t>=SUMIFS(tblInventory[ExtendedValue],tblInventory[Category],"Orthopedic Implants")/SUM(tblInventory[ExtendedValue])</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="48">
-        <f t="array" ref="E8">SUMPRODUCT(('Inventory'!$D$2:$D$258="Orthopedic Implants")*'Inventory'!$J$2:$J$258*'Inventory'!$G$2:$G$258)/SUMPRODUCT('Inventory'!$J$2:$J$258,'Inventory'!$G$2:$G$258)</f>
+      <c r="E8" cm="1" s="47">
+        <f t="array" ref="E8">SUMPRODUCT((Inventory!$D$2:$D$258="Orthopedic Implants")*Inventory!$J$2:$J$258*Inventory!$G$2:$G$258)/SUMPRODUCT(Inventory!$J$2:$J$258,Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -19917,8 +19914,8 @@
           <t>=[@QtyOnHand]&lt;=[@ReorderPoint]</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="44">
-        <f t="array" ref="E9">SUMPRODUCT(--('Inventory'!$J$2:$J$258&lt;='Inventory'!$L$2:$L$258))</f>
+      <c r="E9" cm="1" s="19">
+        <f t="array" ref="E9">SUMPRODUCT(--(Inventory!$J$2:$J$258&lt;=Inventory!$L$2:$L$258))</f>
         <v/>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -19938,7 +19935,7 @@
           <t>Turn on the Table's Total Row and set the LeadTimeDays total to Average. Then, in the yellow cell, type = and click that Total Row cell, so Excel writes a [#Totals] reference. What's the average vendor lead time in days, to 2 decimal places?</t>
         </is>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="48" t="n">
         <v>5.350194552529183</v>
       </c>
       <c r="D10" s="43" t="inlineStr">
@@ -19946,8 +19943,8 @@
           <t>=tblInventory[[#Totals],[LeadTimeDays]]</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="50">
-        <f t="array" ref="E10">AVERAGE('Inventory'!$N$2:$N$258)</f>
+      <c r="E10" cm="1" s="49">
+        <f t="array" ref="E10">AVERAGE(Inventory!$N$2:$N$258)</f>
         <v/>
       </c>
       <c r="F10" s="19" t="inlineStr">
@@ -19986,7 +19983,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="216" customHeight="1">
+    <row r="12" ht="186" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -19997,20 +19994,20 @@
           <t>Insert slicers for Facility and Category (Table Design → Insert Slicer; Mac: Table → Insert Slicer). Select Cedar Ridge Medical Center in the Facility slicer and Surgical in the Category slicer. Set the Total Row's ExtendedValue cell to Sum. What value does it show? Type the number, then clear both slicers, because while they filter the Table the Total Row (and task 6) only summarizes the visible rows.</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="44" t="n">
         <v>47775.51</v>
       </c>
       <c r="D12" s="43" t="inlineStr">
         <is>
-          <t>1. Click inside the Table, then **Table Design → Insert Slicer** (Mac: **Table → Insert Slicer**). Tick **Facility** and **Category** and click **OK**.
-2. In the Facility slicer click **Cedar Ridge Medical Center**. In the Category slicer click **Surgical**. The Table now shows 6 rows.
-3. In the Total Row, click the ExtendedValue cell, open its dropdown, and choose **Sum**.
-4. Read the total and type it in the answer cell: **47,775.51**.
-5. Click the **Clear Filter** button (funnel with a red X) at the top right of each slicer.</t>
-        </is>
-      </c>
-      <c r="E12" cm="1" s="46">
-        <f t="array" ref="E12">SUMPRODUCT(('Inventory'!$H$2:$H$258="Cedar Ridge Medical Center")*('Inventory'!$D$2:$D$258="Surgical")*'Inventory'!$J$2:$J$258*'Inventory'!$G$2:$G$258)</f>
+          <t>1. Click inside the Table, then Table Design → Insert Slicer (Mac: Table → Insert Slicer). Tick Facility and Category and click OK.
+2. In the Facility slicer click Cedar Ridge Medical Center. In the Category slicer click Surgical. The Table now shows 6 rows.
+3. In the Total Row, click the ExtendedValue cell, open its dropdown, and choose Sum.
+4. Read the total and type it in the answer cell: 47,775.51.
+5. Click the Clear Filter button (funnel with a red X) at the top right of each slicer.</t>
+        </is>
+      </c>
+      <c r="E12" cm="1" s="45">
+        <f t="array" ref="E12">SUMPRODUCT((Inventory!$H$2:$H$258="Cedar Ridge Medical Center")*(Inventory!$D$2:$D$258="Surgical")*Inventory!$J$2:$J$258*Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -20019,7 +20016,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="156" customHeight="1">
+    <row r="13" ht="141" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -20030,18 +20027,18 @@
           <t>On the Settings sheet, select A2:B3 and use Formulas → Create from Selection (tick only Left column) to name cell B2 ReportDate and cell B3 ExpiringWindowDays. The gray cell looks up both names and adds them: what date does it show?</t>
         </is>
       </c>
-      <c r="C13" s="51" t="n">
+      <c r="C13" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="D13" s="43" t="inlineStr">
         <is>
-          <t>1. Go to the **Settings** sheet and select **A2:B3** (labels and values together).
-2. Choose **Formulas → Create from Selection** (Windows shortcut: **Ctrl + Shift + F3**).
-3. Tick **Left column** only, untick **Top row**, and click **OK**.
-4. Check the result: click B2 and the Name Box shows **ReportDate**. Open **Formulas → Name Manager** to see both names and what they refer to.</t>
-        </is>
-      </c>
-      <c r="E13" cm="1" s="52">
+          <t>1. Go to the Settings sheet and select A2:B3 (labels and values together).
+2. Choose Formulas → Create from Selection (Windows shortcut: Ctrl + Shift + F3).
+3. Tick Left column only, untick Top row, and click OK.
+4. Check the result: click B2 and the Name Box shows ReportDate. Open Formulas → Name Manager to see both names and what they refer to.</t>
+        </is>
+      </c>
+      <c r="E13" cm="1" s="51">
         <f t="array" ref="E13">Settings!$B$2+Settings!$B$3</f>
         <v/>
       </c>
@@ -20070,8 +20067,8 @@
           <t>=COUNTIFS(tblInventory[ExpirationDate],"&gt;"&amp;ReportDate,tblInventory[ExpirationDate],"&lt;="&amp;ReportDate+ExpiringWindowDays)</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="44">
-        <f t="array" ref="E14">COUNTIFS('Inventory'!$P$2:$P$258,"&gt;"&amp;Settings!$B$2,'Inventory'!$P$2:$P$258,"&lt;="&amp;Settings!$B$2+Settings!$B$3)</f>
+      <c r="E14" cm="1" s="19">
+        <f t="array" ref="E14">COUNTIFS(Inventory!$P$2:$P$258,"&gt;"&amp;Settings!$B$2,Inventory!$P$2:$P$258,"&lt;="&amp;Settings!$B$2+Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -20091,7 +20088,7 @@
           <t>Expired stock must be pulled from the shelves and written off. What's the total ExtendedValue of rows whose ExpirationDate is before ReportDate? Enter it to the cent.</t>
         </is>
       </c>
-      <c r="C15" s="45" t="n">
+      <c r="C15" s="44" t="n">
         <v>17115.69</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
@@ -20099,8 +20096,8 @@
           <t>=SUMIFS(tblInventory[ExtendedValue],tblInventory[ExpirationDate],"&lt;"&amp;ReportDate)</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="46">
-        <f t="array" ref="E15">SUMPRODUCT(('Inventory'!$P$2:$P$258&lt;Settings!$B$2)*('Inventory'!$P$2:$P$258&lt;&gt;"")*'Inventory'!$J$2:$J$258*'Inventory'!$G$2:$G$258)</f>
+      <c r="E15" cm="1" s="45">
+        <f t="array" ref="E15">SUMPRODUCT((Inventory!$P$2:$P$258&lt;Settings!$B$2)*(Inventory!$P$2:$P$258&lt;&gt;"")*Inventory!$J$2:$J$258*Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F15" s="19" t="inlineStr">
@@ -20128,8 +20125,8 @@
           <t>=COUNTIF(tblInventory[LastCountDate],"&lt;"&amp;ReportDate-CycleCountDays)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="44">
-        <f t="array" ref="E16">COUNTIF('Inventory'!$O$2:$O$258,"&lt;"&amp;Settings!$B$2-30)</f>
+      <c r="E16" cm="1" s="19">
+        <f t="array" ref="E16">COUNTIF(Inventory!$O$2:$O$258,"&lt;"&amp;Settings!$B$2-30)</f>
         <v/>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -20161,7 +20158,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -20175,7 +20172,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20219,7 @@
           <t>Add a new column to tblInventory by typing OrderCost in cell T1, just right of the NeedsReorder header. The Table expands to include it. Make it a calculated column that returns ReorderQty × UnitCost for rows where NeedsReorder is TRUE, and 0 for every other row. The gray cell totals the column: what's the total cost of this week's orders?</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="44" t="n">
         <v>173950.91</v>
       </c>
       <c r="D5" s="43" t="inlineStr">
@@ -20230,13 +20227,13 @@
           <t>=IF([@NeedsReorder],[@ReorderQty]*[@UnitCost],0)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
-        <f t="array" ref="E5">SUMPRODUCT(('Inventory'!$J$2:$J$258&lt;='Inventory'!$L$2:$L$258)*'Inventory'!$M$2:$M$258*'Inventory'!$G$2:$G$258)</f>
+      <c r="E5" cm="1" s="45">
+        <f t="array" ref="E5">SUMPRODUCT((Inventory!$J$2:$J$258&lt;=Inventory!$L$2:$L$258)*Inventory!$M$2:$M$258*Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Typing in the first empty column next to a Table adds a column to it (Excel's *AutoExpansion*). IF([@NeedsReorder],…) reuses the calculated column you built in task 5 instead of repeating the comparison. The 41 rows that need an order return their cost and the rest return 0, so the column total is the cost of the whole report.</t>
+          <t>Typing in the first empty column next to a Table adds a column to it (Excel's AutoExpansion). IF([@NeedsReorder],…) reuses the calculated column you built in task 5 instead of repeating the comparison. The 41 rows that need an order return their cost and the rest return 0, so the column total is the cost of the whole report.</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20265,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from *another* Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) works too in Excel 2021 or Microsoft 365. All four reorder lines for Summit Orthopedic Systems are orthopedic implants, and three of them cost more than $2,000 per unit, so a handful of lines makes the largest order.</t>
+          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from another Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) works too in Excel 2021 or Microsoft 365. All four reorder lines for Summit Orthopedic Systems are orthopedic implants, and three of them cost more than $2,000 per unit, so a handful of lines makes the largest order.</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20280,7 @@
           <t>What's the value of that vendor's purchase order, to the cent?</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="44" t="n">
         <v>62855.33</v>
       </c>
       <c r="D7" s="43" t="inlineStr">
@@ -20291,8 +20288,8 @@
           <t>=MAX(tblVendors[ReorderCost])</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="46">
-        <f t="array" ref="E7">SUMPRODUCT(('Inventory'!$E$2:$E$258="Summit Orthopedic Systems")*('Inventory'!$J$2:$J$258&lt;='Inventory'!$L$2:$L$258)*'Inventory'!$M$2:$M$258*'Inventory'!$G$2:$G$258)</f>
+      <c r="E7" cm="1" s="45">
+        <f t="array" ref="E7">SUMPRODUCT((Inventory!$E$2:$E$258="Summit Orthopedic Systems")*(Inventory!$J$2:$J$258&lt;=Inventory!$L$2:$L$258)*Inventory!$M$2:$M$258*Inventory!$G$2:$G$258)</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -20312,7 +20309,7 @@
           <t>The group purchasing contract gives a 2% discount on any single vendor order of $20,000 or more. Define two named constants, DiscountMin (=20000) and DiscountPct (=0.02), then calculate the total discount on this week's orders, to the cent.</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="44" t="n">
         <v>2431.66</v>
       </c>
       <c r="D8" s="43" t="inlineStr">

--- a/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
+++ b/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C31"/>
+  <dimension ref="B2:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Intermediate  ·  about 50 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Intermediate  ·  about 105 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -956,58 +956,82 @@
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Data: 257 rows</t>
+          <t>12 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 2 rows</t>
+          <t>Data: 257 rows</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Data: 2 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Data: 7 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Supply inventory snapshot for 15 storerooms across three Bluestone hospitals (257 stock rows, as of 12/31/2025), a Settings sheet with the report date and expiry window, and Purchasing's vendor list.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (4 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Supply inventory snapshot for 15 storerooms across three Bluestone hospitals (257 stock rows, as of 12/31/2025), a Settings sheet with the report date and expiry window, and Purchasing's vendor list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
+++ b/03-data-analysis/01-tables-named-ranges/3.1-tables-named-ranges.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Practice" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Vendors" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bonus" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bonus" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vendors" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Answer Key" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="Bonus Key" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
@@ -829,7 +829,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -837,7 +837,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 1, 3, 5, and 9, do the work on the Inventory or Settings sheet instead, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>The Inventory, Settings, and Vendors sheets are plain ranges on purpose. You turn them into Tables and named cells as part of the practice.</t>
+          <t>The Inventory, Settings, and Vendors sheets are plain ranges on purpose. You turn them into Tables and named cells as part of the practice and the bonus.</t>
         </is>
       </c>
     </row>
@@ -992,24 +992,24 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 7 rows</t>
+          <t>The bonus challenge (4 parts).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Vendors</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (4 parts).</t>
+          <t>Data: 7 rows</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>Type a formula or value in each yellow cell. For tasks 1, 3, 5, and 9, do the work on the Inventory or Settings sheet instead, and the gray cell here reads it. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Table Design → Total Row (Windows: Ctrl + Shift + T; Mac: Table → Total Row), then use the dropdown in the Total Row cell</t>
+          <t>Table Design → Total Row (Windows: Ctrl + Shift + T; Mac: Table → Total Row), then use the drop-down arrow in the Total Row cell</t>
         </is>
       </c>
       <c r="D11" s="26" t="n"/>
@@ -1299,7 +1299,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="51" customHeight="1">
+    <row r="14" ht="66" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -19424,140 +19424,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="inlineStr">
-        <is>
-          <t>AccountNo</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>ReorderCost</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Apex Surgical Co.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BHS-V1001</t>
-        </is>
-      </c>
-      <c r="C2" s="33" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CareLine Distributors</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BHS-V1002</t>
-        </is>
-      </c>
-      <c r="C3" s="33" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Harbor Health Products</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BHS-V1003</t>
-        </is>
-      </c>
-      <c r="C4" s="33" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Keystone Lab Solutions</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BHS-V1004</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Northstar Medical Supply</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BHS-V1005</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pinnacle Biomedical</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BHS-V1006</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Summit Orthopedic Systems</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BHS-V1007</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Bonus: convert this list to a Table named tblVendors, then fill ReorderCost with a calculated column.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="00BF9000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -19586,10 +19452,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="49" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>Type a formula or value in each yellow cell. For B1, fill the OrderCost column on the Inventory sheet instead, and the gray cell here reads it. B2 also builds the tblVendors Table on the Vendors sheet. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
@@ -19733,6 +19599,140 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>AccountNo</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>ReorderCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apex Surgical Co.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BHS-V1001</t>
+        </is>
+      </c>
+      <c r="C2" s="33" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CareLine Distributors</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BHS-V1002</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Harbor Health Products</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BHS-V1003</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Keystone Lab Solutions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BHS-V1004</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Northstar Medical Supply</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BHS-V1005</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pinnacle Biomedical</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BHS-V1006</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Summit Orthopedic Systems</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BHS-V1007</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Bonus: convert this list to a Table named tblVendors, then fill ReorderCost with a calculated column.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -19973,7 +19973,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>The Total Row's dropdown writes =SUBTOTAL(101,[LeadTimeDays]). Function number 101 means AVERAGE of the visible rows only, ignoring rows hidden by a filter or hidden by hand (109 = SUM, 103 = COUNTA, 104 = MAX). tblInventory[[#Totals],[LeadTimeDays]] points at that total cell by name, so it still works if rows are added. If you turn the Total Row off, the reference returns #REF!.</t>
+          <t>The Total Row's drop-down list writes =SUBTOTAL(101,[LeadTimeDays]). Function number 101 means AVERAGE of the visible rows only, ignoring rows hidden by a filter or hidden by hand (109 = SUM, 103 = COUNTA, 104 = MAX). tblInventory[[#Totals],[LeadTimeDays]] points at that total cell by name, so it still works if rows are added. If you turn the Total Row off, the reference returns #REF!.</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="186" customHeight="1">
+    <row r="12" ht="201" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -20025,7 +20025,7 @@
         <is>
           <t>1. Click inside the Table, then Table Design → Insert Slicer (Mac: Table → Insert Slicer). Tick Facility and Category and click OK.
 2. In the Facility slicer click Cedar Ridge Medical Center. In the Category slicer click Surgical. The Table now shows 6 rows.
-3. In the Total Row, click the ExtendedValue cell, open its dropdown, and choose Sum.
+3. In the Total Row, click the ExtendedValue cell, open its drop-down list, and choose Sum.
 4. Read the total and type it in the answer cell: 47,775.51.
 5. Click the Clear Filter button (funnel with a red X) at the top right of each slicer.</t>
         </is>
@@ -20261,7 +20261,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="156" customHeight="1">
+    <row r="6" ht="171" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from another Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) works too in Excel 2021 or Microsoft 365. All four reorder lines for Summit Orthopedic Systems are orthopedic implants, and three of them cost more than $2,000 per unit, so a handful of lines makes the largest order.</t>
+          <t>The calculated column in tblVendors is =SUMIFS(tblInventory[OrderCost],tblInventory[Vendor],[@Vendor]). It mixes whole columns from another Table with [@Vendor] from this row, which is how Tables talk to each other. INDEX/MATCH (Lesson 2.6) then returns the vendor on the row with the largest total. =XLOOKUP(MAX(tblVendors[ReorderCost]),tblVendors[ReorderCost],tblVendors[Vendor]) also works in Microsoft 365 and Excel 2021 or later. All four reorder lines for Summit Orthopedic Systems are orthopedic implants, and three of them cost more than $2,000 per unit, so a handful of lines makes the largest order.</t>
         </is>
       </c>
     </row>
